--- a/Shiny/Datos limpios/pricing_diario_girasol_2025.xlsx
+++ b/Shiny/Datos limpios/pricing_diario_girasol_2025.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K246"/>
+  <dimension ref="A1:K267"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -9451,33 +9451,810 @@
         <v>45957</v>
       </c>
       <c r="B246">
-        <v>950</v>
+        <v>17061.72</v>
       </c>
       <c r="C246">
         <v>0</v>
       </c>
       <c r="D246">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E246">
-        <v>950</v>
+        <v>16911.72</v>
       </c>
       <c r="F246">
-        <v>0</v>
+        <v>1377.62</v>
       </c>
       <c r="G246">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H246">
         <v>0</v>
       </c>
       <c r="I246">
-        <v>0</v>
+        <v>1418.62</v>
       </c>
       <c r="J246">
-        <v>950</v>
+        <v>18330.34</v>
       </c>
       <c r="K246" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2">
+        <v>45958</v>
+      </c>
+      <c r="B247">
+        <v>14226.73</v>
+      </c>
+      <c r="C247">
+        <v>110</v>
+      </c>
+      <c r="D247">
+        <v>3588</v>
+      </c>
+      <c r="E247">
+        <v>10748.73</v>
+      </c>
+      <c r="F247">
+        <v>260</v>
+      </c>
+      <c r="G247">
+        <v>0</v>
+      </c>
+      <c r="H247">
+        <v>0</v>
+      </c>
+      <c r="I247">
+        <v>260</v>
+      </c>
+      <c r="J247">
+        <v>11008.73</v>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2">
+        <v>45959</v>
+      </c>
+      <c r="B248">
+        <v>10794.99</v>
+      </c>
+      <c r="C248">
+        <v>5.38</v>
+      </c>
+      <c r="D248">
+        <v>170</v>
+      </c>
+      <c r="E248">
+        <v>10630.37</v>
+      </c>
+      <c r="F248">
+        <v>140.57</v>
+      </c>
+      <c r="G248">
+        <v>0</v>
+      </c>
+      <c r="H248">
+        <v>0</v>
+      </c>
+      <c r="I248">
+        <v>140.57</v>
+      </c>
+      <c r="J248">
+        <v>10770.94</v>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2">
+        <v>45960</v>
+      </c>
+      <c r="B249">
+        <v>10922.15</v>
+      </c>
+      <c r="C249">
+        <v>10.9</v>
+      </c>
+      <c r="D249">
+        <v>560</v>
+      </c>
+      <c r="E249">
+        <v>10373.05</v>
+      </c>
+      <c r="F249">
+        <v>1145.51</v>
+      </c>
+      <c r="G249">
+        <v>0</v>
+      </c>
+      <c r="H249">
+        <v>0</v>
+      </c>
+      <c r="I249">
+        <v>1145.51</v>
+      </c>
+      <c r="J249">
+        <v>11518.56</v>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B250">
+        <v>8002.37</v>
+      </c>
+      <c r="C250">
+        <v>30.62</v>
+      </c>
+      <c r="D250">
+        <v>0</v>
+      </c>
+      <c r="E250">
+        <v>8032.99</v>
+      </c>
+      <c r="F250">
+        <v>0</v>
+      </c>
+      <c r="G250">
+        <v>0</v>
+      </c>
+      <c r="H250">
+        <v>0</v>
+      </c>
+      <c r="I250">
+        <v>0</v>
+      </c>
+      <c r="J250">
+        <v>8032.99</v>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B251">
+        <v>8369.34</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+      <c r="D251">
+        <v>0</v>
+      </c>
+      <c r="E251">
+        <v>8369.34</v>
+      </c>
+      <c r="F251">
+        <v>627.3099999999999</v>
+      </c>
+      <c r="G251">
+        <v>0</v>
+      </c>
+      <c r="H251">
+        <v>0</v>
+      </c>
+      <c r="I251">
+        <v>627.3099999999999</v>
+      </c>
+      <c r="J251">
+        <v>8996.65</v>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2">
+        <v>45965</v>
+      </c>
+      <c r="B252">
+        <v>30234.25</v>
+      </c>
+      <c r="C252">
+        <v>0</v>
+      </c>
+      <c r="D252">
+        <v>30.62</v>
+      </c>
+      <c r="E252">
+        <v>30203.63</v>
+      </c>
+      <c r="F252">
+        <v>1015</v>
+      </c>
+      <c r="G252">
+        <v>0</v>
+      </c>
+      <c r="H252">
+        <v>0</v>
+      </c>
+      <c r="I252">
+        <v>1015</v>
+      </c>
+      <c r="J252">
+        <v>31218.63</v>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2">
+        <v>45966</v>
+      </c>
+      <c r="B253">
+        <v>21777.76</v>
+      </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
+      <c r="D253">
+        <v>1000</v>
+      </c>
+      <c r="E253">
+        <v>20777.76</v>
+      </c>
+      <c r="F253">
+        <v>1353.12</v>
+      </c>
+      <c r="G253">
+        <v>0</v>
+      </c>
+      <c r="H253">
+        <v>0</v>
+      </c>
+      <c r="I253">
+        <v>1353.12</v>
+      </c>
+      <c r="J253">
+        <v>22130.88</v>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2">
+        <v>45967</v>
+      </c>
+      <c r="B254">
+        <v>7089.08</v>
+      </c>
+      <c r="C254">
+        <v>0</v>
+      </c>
+      <c r="D254">
+        <v>13180</v>
+      </c>
+      <c r="E254">
+        <v>-6090.92</v>
+      </c>
+      <c r="F254">
+        <v>326.08</v>
+      </c>
+      <c r="G254">
+        <v>0</v>
+      </c>
+      <c r="H254">
+        <v>0</v>
+      </c>
+      <c r="I254">
+        <v>326.08</v>
+      </c>
+      <c r="J254">
+        <v>-5764.84</v>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B255">
+        <v>9011.860000000001</v>
+      </c>
+      <c r="C255">
+        <v>500</v>
+      </c>
+      <c r="D255">
+        <v>591</v>
+      </c>
+      <c r="E255">
+        <v>8920.860000000001</v>
+      </c>
+      <c r="F255">
+        <v>392.92</v>
+      </c>
+      <c r="G255">
+        <v>0</v>
+      </c>
+      <c r="H255">
+        <v>0</v>
+      </c>
+      <c r="I255">
+        <v>392.92</v>
+      </c>
+      <c r="J255">
+        <v>9313.780000000001</v>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2">
+        <v>45969</v>
+      </c>
+      <c r="B256">
+        <v>15</v>
+      </c>
+      <c r="C256">
+        <v>0</v>
+      </c>
+      <c r="D256">
+        <v>0</v>
+      </c>
+      <c r="E256">
+        <v>15</v>
+      </c>
+      <c r="F256">
+        <v>0</v>
+      </c>
+      <c r="G256">
+        <v>0</v>
+      </c>
+      <c r="H256">
+        <v>0</v>
+      </c>
+      <c r="I256">
+        <v>0</v>
+      </c>
+      <c r="J256">
+        <v>15</v>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B257">
+        <v>9390.530000000001</v>
+      </c>
+      <c r="C257">
+        <v>0</v>
+      </c>
+      <c r="D257">
+        <v>1070</v>
+      </c>
+      <c r="E257">
+        <v>8320.530000000001</v>
+      </c>
+      <c r="F257">
+        <v>139.7</v>
+      </c>
+      <c r="G257">
+        <v>0</v>
+      </c>
+      <c r="H257">
+        <v>0</v>
+      </c>
+      <c r="I257">
+        <v>139.7</v>
+      </c>
+      <c r="J257">
+        <v>8460.230000000001</v>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B258">
+        <v>15567.05</v>
+      </c>
+      <c r="C258">
+        <v>0</v>
+      </c>
+      <c r="D258">
+        <v>0</v>
+      </c>
+      <c r="E258">
+        <v>15567.05</v>
+      </c>
+      <c r="F258">
+        <v>346.18</v>
+      </c>
+      <c r="G258">
+        <v>0</v>
+      </c>
+      <c r="H258">
+        <v>0</v>
+      </c>
+      <c r="I258">
+        <v>346.18</v>
+      </c>
+      <c r="J258">
+        <v>15913.23</v>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B259">
+        <v>11267.99</v>
+      </c>
+      <c r="C259">
+        <v>0</v>
+      </c>
+      <c r="D259">
+        <v>236.69</v>
+      </c>
+      <c r="E259">
+        <v>11031.3</v>
+      </c>
+      <c r="F259">
+        <v>531.5599999999999</v>
+      </c>
+      <c r="G259">
+        <v>0</v>
+      </c>
+      <c r="H259">
+        <v>0</v>
+      </c>
+      <c r="I259">
+        <v>531.5599999999999</v>
+      </c>
+      <c r="J259">
+        <v>11562.86</v>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2">
+        <v>45974</v>
+      </c>
+      <c r="B260">
+        <v>7976.63</v>
+      </c>
+      <c r="C260">
+        <v>1950</v>
+      </c>
+      <c r="D260">
+        <v>0</v>
+      </c>
+      <c r="E260">
+        <v>9926.630000000001</v>
+      </c>
+      <c r="F260">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="G260">
+        <v>0</v>
+      </c>
+      <c r="H260">
+        <v>0</v>
+      </c>
+      <c r="I260">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="J260">
+        <v>9993.230000000001</v>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B261">
+        <v>9603.01</v>
+      </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
+      <c r="D261">
+        <v>220</v>
+      </c>
+      <c r="E261">
+        <v>9383.01</v>
+      </c>
+      <c r="F261">
+        <v>624.0700000000001</v>
+      </c>
+      <c r="G261">
+        <v>0</v>
+      </c>
+      <c r="H261">
+        <v>0</v>
+      </c>
+      <c r="I261">
+        <v>624.0700000000001</v>
+      </c>
+      <c r="J261">
+        <v>10007.08</v>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2">
+        <v>45977</v>
+      </c>
+      <c r="B262">
+        <v>0</v>
+      </c>
+      <c r="C262">
+        <v>0</v>
+      </c>
+      <c r="D262">
+        <v>0</v>
+      </c>
+      <c r="E262">
+        <v>0</v>
+      </c>
+      <c r="F262">
+        <v>800.28</v>
+      </c>
+      <c r="G262">
+        <v>0</v>
+      </c>
+      <c r="H262">
+        <v>0</v>
+      </c>
+      <c r="I262">
+        <v>800.28</v>
+      </c>
+      <c r="J262">
+        <v>800.28</v>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B263">
+        <v>8514.66</v>
+      </c>
+      <c r="C263">
+        <v>155</v>
+      </c>
+      <c r="D263">
+        <v>0</v>
+      </c>
+      <c r="E263">
+        <v>8669.66</v>
+      </c>
+      <c r="F263">
+        <v>180</v>
+      </c>
+      <c r="G263">
+        <v>0</v>
+      </c>
+      <c r="H263">
+        <v>0</v>
+      </c>
+      <c r="I263">
+        <v>180</v>
+      </c>
+      <c r="J263">
+        <v>8849.66</v>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B264">
+        <v>7518.94</v>
+      </c>
+      <c r="C264">
+        <v>0</v>
+      </c>
+      <c r="D264">
+        <v>1100</v>
+      </c>
+      <c r="E264">
+        <v>6418.94</v>
+      </c>
+      <c r="F264">
+        <v>247.16</v>
+      </c>
+      <c r="G264">
+        <v>0</v>
+      </c>
+      <c r="H264">
+        <v>0</v>
+      </c>
+      <c r="I264">
+        <v>247.16</v>
+      </c>
+      <c r="J264">
+        <v>6666.099999999999</v>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B265">
+        <v>15124.94</v>
+      </c>
+      <c r="C265">
+        <v>600</v>
+      </c>
+      <c r="D265">
+        <v>12</v>
+      </c>
+      <c r="E265">
+        <v>15712.94</v>
+      </c>
+      <c r="F265">
+        <v>220</v>
+      </c>
+      <c r="G265">
+        <v>0</v>
+      </c>
+      <c r="H265">
+        <v>0</v>
+      </c>
+      <c r="I265">
+        <v>220</v>
+      </c>
+      <c r="J265">
+        <v>15932.94</v>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B266">
+        <v>9248.07</v>
+      </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
+      <c r="D266">
+        <v>0</v>
+      </c>
+      <c r="E266">
+        <v>9248.07</v>
+      </c>
+      <c r="F266">
+        <v>442.21</v>
+      </c>
+      <c r="G266">
+        <v>0</v>
+      </c>
+      <c r="H266">
+        <v>0</v>
+      </c>
+      <c r="I266">
+        <v>442.21</v>
+      </c>
+      <c r="J266">
+        <v>9690.279999999999</v>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B267">
+        <v>1759.36</v>
+      </c>
+      <c r="C267">
+        <v>0</v>
+      </c>
+      <c r="D267">
+        <v>0</v>
+      </c>
+      <c r="E267">
+        <v>1759.36</v>
+      </c>
+      <c r="F267">
+        <v>496.94</v>
+      </c>
+      <c r="G267">
+        <v>0</v>
+      </c>
+      <c r="H267">
+        <v>0</v>
+      </c>
+      <c r="I267">
+        <v>496.94</v>
+      </c>
+      <c r="J267">
+        <v>2256.3</v>
+      </c>
+      <c r="K267" t="inlineStr">
         <is>
           <t>GIRASOL</t>
         </is>
